--- a/output/laminas_comunales/comunal_o_ocup_a_2020_los_rios.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2020_los_rios.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>38.0895790129587</v>
+        <v>58.7370884368522</v>
       </c>
     </row>
     <row r="3">
@@ -399,67 +399,67 @@
         </is>
       </c>
       <c r="C3">
-        <v>34.5986191562811</v>
+        <v>57.4787636030623</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Máfil</t>
         </is>
       </c>
       <c r="C4">
-        <v>33.564285496509</v>
+        <v>54.1313918049441</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Máfil</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="C5">
-        <v>32.8871843039031</v>
+        <v>53.1158860868073</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lanco</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="C6">
-        <v>32.8817453817454</v>
+        <v>51.9728951786999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mariquina</t>
+          <t>Paillaco</t>
         </is>
       </c>
       <c r="C7">
-        <v>32.4495276459023</v>
+        <v>51.81598062954</v>
       </c>
     </row>
     <row r="8">
@@ -474,82 +474,1267 @@
         </is>
       </c>
       <c r="C8">
-        <v>31.7374541777272</v>
+        <v>51.4699211884107</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paillaco</t>
+          <t>Lanco</t>
         </is>
       </c>
       <c r="C9">
-        <v>31.3990170192146</v>
+        <v>50.8658008658009</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Futrono</t>
+          <t>Corral</t>
         </is>
       </c>
       <c r="C10">
-        <v>30.0960878517502</v>
+        <v>50.8541793776693</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Corral</t>
+          <t>Mariquina</t>
         </is>
       </c>
       <c r="C11">
-        <v>29.0965655573294</v>
+        <v>50.4006880106329</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="C12">
-        <v>27.3800612453215</v>
+        <v>49.5749051672413</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>45.5331654072208</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>45.3529797509606</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>44.9013063244519</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>44.0474283867886</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>43.0068716771907</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>42.9678782081939</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>42.8066476497582</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>42.2140658897129</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>42.2001597626384</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>41.3107966133119</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>41.2247474747475</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>40.9013605442177</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>14203</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Lago Ranco</t>
         </is>
       </c>
-      <c r="C13">
+      <c r="C25">
+        <v>40.5174713256868</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>40.4671104331346</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>39.9100607382028</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>39.8392015525367</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>39.821449208367</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>39.1879246511249</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>38.614382258913</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>38.5811704834606</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>38.4435881012977</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>38.0895790129587</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>37.668720054757</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>37.485779294653</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>36.8393154626685</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>35.7816377171216</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>34.5986191562811</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>34.2175623158906</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>33.608117816092</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>33.564285496509</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>33.541706197775</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>33.4308327598073</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>33.2223339197453</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>32.8871843039031</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>32.8817453817454</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>32.5378527185134</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>32.4495276459023</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>31.9800396121809</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>31.7374541777272</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>31.3990170192146</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>31.37102014295</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>30.9466984884646</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>30.8503012485482</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>30.7437243175068</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>30.4408326839586</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>30.3990044958253</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>30.0960878517502</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>29.8046077573637</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>29.3754272878211</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>29.0965655573294</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>28.0058161708619</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>27.9475982532751</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>27.3800612453215</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>26.0486001056524</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>26.0214827295703</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>25.5308426286789</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>25.1380212810667</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C70">
         <v>24.7293845779616</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>24.6697315578102</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>24.6134318024463</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>24.4891518737673</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>23.9792775478021</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>23.9452543885748</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>22.7753956910698</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>22.5463976011022</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>22.3368102288022</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>18.7573223447663</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>9.64591363428497</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>9.516260162601631</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>9.205524707942759</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>8.89294051114881</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>8.52965488737342</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>8.437702122655381</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>7.77840748087277</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>7.77076023391813</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>7.08467309753483</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>6.97337962962963</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>6.95025234318673</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>6.64585191793042</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>5.80515670835263</v>
       </c>
     </row>
   </sheetData>
